--- a/Inventario_Rutas_Maule_Completo.xlsx
+++ b/Inventario_Rutas_Maule_Completo.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joset\OneDrive\Desktop\Nueva carpeta (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joset\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA25859-6995-4D9C-B1B1-F81C48A5CE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9E7D69-B47A-47E8-A78A-124D0DF44D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
@@ -519,1015 +516,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>I-300-J</v>
-          </cell>
-          <cell r="B2">
-            <v>7619.0483645064787</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>J-25</v>
-          </cell>
-          <cell r="B3">
-            <v>10351.93701813308</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>J-40</v>
-          </cell>
-          <cell r="B4">
-            <v>72200.438137957812</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>J-415</v>
-          </cell>
-          <cell r="B5">
-            <v>6317.4165120732696</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>J-446</v>
-          </cell>
-          <cell r="B6">
-            <v>2262.6284902330058</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>J-448</v>
-          </cell>
-          <cell r="B7">
-            <v>10164.07724344292</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>J-52-K</v>
-          </cell>
-          <cell r="B8">
-            <v>19368.336953576742</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>J-55</v>
-          </cell>
-          <cell r="B9">
-            <v>49815.50482857976</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>J-550</v>
-          </cell>
-          <cell r="B10">
-            <v>12250.26732338182</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>J-580</v>
-          </cell>
-          <cell r="B11">
-            <v>4948.1140912628043</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>J-582</v>
-          </cell>
-          <cell r="B12">
-            <v>1582.373909739084</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>J-591</v>
-          </cell>
-          <cell r="B13">
-            <v>1367.6966510538639</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>J-60</v>
-          </cell>
-          <cell r="B14">
-            <v>93919.524354428388</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>J-620</v>
-          </cell>
-          <cell r="B15">
-            <v>11948.086781785079</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>J-624</v>
-          </cell>
-          <cell r="B16">
-            <v>189548.06202502971</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>J-640</v>
-          </cell>
-          <cell r="B17">
-            <v>3988.1309129103861</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>J-645</v>
-          </cell>
-          <cell r="B18">
-            <v>3371.0139577269729</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>J-65</v>
-          </cell>
-          <cell r="B19">
-            <v>43024.962376204312</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>J-665</v>
-          </cell>
-          <cell r="B20">
-            <v>5329.4229054158404</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>J-70-I</v>
-          </cell>
-          <cell r="B21">
-            <v>1304.771666666667</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>J-730</v>
-          </cell>
-          <cell r="B22">
-            <v>8217.7890665854538</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>J-743</v>
-          </cell>
-          <cell r="B23">
-            <v>5581.8228093440794</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>J-75-K</v>
-          </cell>
-          <cell r="B24">
-            <v>21831.927681984271</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>J-76-K</v>
-          </cell>
-          <cell r="B25">
-            <v>52757.050324769218</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>J-77</v>
-          </cell>
-          <cell r="B26">
-            <v>9361.7908776452696</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>J-80</v>
-          </cell>
-          <cell r="B27">
-            <v>13815.300838874749</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>J-810</v>
-          </cell>
-          <cell r="B28">
-            <v>1435.3962969289489</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>J-82</v>
-          </cell>
-          <cell r="B29">
-            <v>900.52823916286729</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>J-820</v>
-          </cell>
-          <cell r="B30">
-            <v>6234.0746979889091</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>J-830</v>
-          </cell>
-          <cell r="B31">
-            <v>3242.3081745541072</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>J-850</v>
-          </cell>
-          <cell r="B32">
-            <v>482.37910440169452</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>K-11</v>
-          </cell>
-          <cell r="B33">
-            <v>5992.2399058473693</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>K-113</v>
-          </cell>
-          <cell r="B34">
-            <v>1082.474698389354</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>K-120</v>
-          </cell>
-          <cell r="B35">
-            <v>7717.1002948804489</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>K-121</v>
-          </cell>
-          <cell r="B36">
-            <v>726.85382758346645</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>K-125</v>
-          </cell>
-          <cell r="B37">
-            <v>4104.2270222378784</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>K-155</v>
-          </cell>
-          <cell r="B38">
-            <v>830.36812317638282</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>K-170</v>
-          </cell>
-          <cell r="B39">
-            <v>976.76167199999998</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>K-180</v>
-          </cell>
-          <cell r="B40">
-            <v>179431.96411190819</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41" t="str">
-            <v>K-25</v>
-          </cell>
-          <cell r="B41">
-            <v>19630.131033602502</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42" t="str">
-            <v>K-275</v>
-          </cell>
-          <cell r="B42">
-            <v>1791.3023261411879</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>K-30</v>
-          </cell>
-          <cell r="B43">
-            <v>724.45718474620548</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44" t="str">
-            <v>K-35</v>
-          </cell>
-          <cell r="B44">
-            <v>67846.952110057697</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45" t="str">
-            <v>K-353</v>
-          </cell>
-          <cell r="B45">
-            <v>5567.75982729321</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46" t="str">
-            <v>K-361</v>
-          </cell>
-          <cell r="B46">
-            <v>3532.2193312939939</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47" t="str">
-            <v>K-363</v>
-          </cell>
-          <cell r="B47">
-            <v>1992.403732324485</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>K-365</v>
-          </cell>
-          <cell r="B48">
-            <v>850.71241505968783</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49" t="str">
-            <v>K-375</v>
-          </cell>
-          <cell r="B49">
-            <v>2390.432140429954</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50" t="str">
-            <v>K-40-J</v>
-          </cell>
-          <cell r="B50">
-            <v>4983.3850618385641</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51" t="str">
-            <v>K-405</v>
-          </cell>
-          <cell r="B51">
-            <v>25422.034201961818</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52" t="str">
-            <v>K-427</v>
-          </cell>
-          <cell r="B52">
-            <v>3097.7968420897369</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53" t="str">
-            <v>K-429</v>
-          </cell>
-          <cell r="B53">
-            <v>2447.8561655805638</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54" t="str">
-            <v>K-455</v>
-          </cell>
-          <cell r="B54">
-            <v>9855.9842995581421</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55" t="str">
-            <v>K-505</v>
-          </cell>
-          <cell r="B55">
-            <v>12856.677238693061</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56" t="str">
-            <v>K-509</v>
-          </cell>
-          <cell r="B56">
-            <v>7085.7481211057466</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57" t="str">
-            <v>K-60-J</v>
-          </cell>
-          <cell r="B57">
-            <v>55734.761525780843</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>K-630</v>
-          </cell>
-          <cell r="B58">
-            <v>8959.5249647001529</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59" t="str">
-            <v>K-688</v>
-          </cell>
-          <cell r="B59">
-            <v>44.585141077055283</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60" t="str">
-            <v>K-78-M</v>
-          </cell>
-          <cell r="B60">
-            <v>69495.254216778834</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61" t="str">
-            <v>L-11</v>
-          </cell>
-          <cell r="B61">
-            <v>30951.33420428856</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62" t="str">
-            <v>L-139</v>
-          </cell>
-          <cell r="B62">
-            <v>4102.2215134370581</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63" t="str">
-            <v>L-151</v>
-          </cell>
-          <cell r="B63">
-            <v>7665.1918300325251</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64" t="str">
-            <v>L-160</v>
-          </cell>
-          <cell r="B64">
-            <v>49652.707851877531</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65" t="str">
-            <v>L-165</v>
-          </cell>
-          <cell r="B65">
-            <v>1649.9862670250361</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66" t="str">
-            <v>L-171</v>
-          </cell>
-          <cell r="B66">
-            <v>5573.9897451540292</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67" t="str">
-            <v>L-191</v>
-          </cell>
-          <cell r="B67">
-            <v>6717.8558496128171</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68" t="str">
-            <v>L-202</v>
-          </cell>
-          <cell r="B68">
-            <v>3673.9642246980379</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69" t="str">
-            <v>L-212</v>
-          </cell>
-          <cell r="B69">
-            <v>253.85420844413801</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70" t="str">
-            <v>L-25</v>
-          </cell>
-          <cell r="B70">
-            <v>35665.43809510018</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71" t="str">
-            <v>L-270</v>
-          </cell>
-          <cell r="B71">
-            <v>5089.8657090909073</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72" t="str">
-            <v>L-291</v>
-          </cell>
-          <cell r="B72">
-            <v>2807.8942847058411</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73" t="str">
-            <v>L-30-K</v>
-          </cell>
-          <cell r="B73">
-            <v>149104.5441978325</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74" t="str">
-            <v>L-311</v>
-          </cell>
-          <cell r="B74">
-            <v>9449.1127267722532</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75" t="str">
-            <v>L-32</v>
-          </cell>
-          <cell r="B75">
-            <v>15335.356975078999</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76" t="str">
-            <v>L-333</v>
-          </cell>
-          <cell r="B76">
-            <v>1355.5832818502481</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77" t="str">
-            <v>L-366</v>
-          </cell>
-          <cell r="B77">
-            <v>7045.1438083273497</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78" t="str">
-            <v>L-370</v>
-          </cell>
-          <cell r="B78">
-            <v>1100.3449358375769</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79" t="str">
-            <v>L-374</v>
-          </cell>
-          <cell r="B79">
-            <v>287.74363818456021</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80" t="str">
-            <v>L-390-M</v>
-          </cell>
-          <cell r="B80">
-            <v>614.5167396174337</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81" t="str">
-            <v>L-391</v>
-          </cell>
-          <cell r="B81">
-            <v>2993.828399940784</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82" t="str">
-            <v>L-429</v>
-          </cell>
-          <cell r="B82">
-            <v>1043.4499458197879</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83" t="str">
-            <v>L-45</v>
-          </cell>
-          <cell r="B83">
-            <v>9739.9071363956209</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84" t="str">
-            <v>L-475</v>
-          </cell>
-          <cell r="B84">
-            <v>500.1647038676619</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85" t="str">
-            <v>L-491</v>
-          </cell>
-          <cell r="B85">
-            <v>5830.6457879304053</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86" t="str">
-            <v>L-510</v>
-          </cell>
-          <cell r="B86">
-            <v>350.63398610770378</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87" t="str">
-            <v>L-535</v>
-          </cell>
-          <cell r="B87">
-            <v>6122.4369765857291</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88" t="str">
-            <v>L-551</v>
-          </cell>
-          <cell r="B88">
-            <v>20257.88498724798</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89" t="str">
-            <v>L-600</v>
-          </cell>
-          <cell r="B89">
-            <v>8347.4716027707109</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90" t="str">
-            <v>L-642</v>
-          </cell>
-          <cell r="B90">
-            <v>2400.4270235909471</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91" t="str">
-            <v>L-665</v>
-          </cell>
-          <cell r="B91">
-            <v>1225.552589242749</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92" t="str">
-            <v>L-700</v>
-          </cell>
-          <cell r="B92">
-            <v>312426.03767695627</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93" t="str">
-            <v>L-751</v>
-          </cell>
-          <cell r="B93">
-            <v>9211.3752871367524</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94" t="str">
-            <v>L-779</v>
-          </cell>
-          <cell r="B94">
-            <v>1218.450561052719</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95" t="str">
-            <v>L-851</v>
-          </cell>
-          <cell r="B95">
-            <v>7647.8277402915446</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96" t="str">
-            <v>L-877</v>
-          </cell>
-          <cell r="B96">
-            <v>1560.984478666013</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97" t="str">
-            <v>M-420-K</v>
-          </cell>
-          <cell r="B97">
-            <v>255.467650523966</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98" t="str">
-            <v>M-450-k</v>
-          </cell>
-          <cell r="B98">
-            <v>350.27415493806342</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99" t="str">
-            <v>M-50-K</v>
-          </cell>
-          <cell r="B99">
-            <v>48711.920920181721</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100" t="str">
-            <v>M-500</v>
-          </cell>
-          <cell r="B100">
-            <v>1582.0808604981021</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101" t="str">
-            <v>M-520-L</v>
-          </cell>
-          <cell r="B101">
-            <v>1303.402855759472</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102" t="str">
-            <v>M-570</v>
-          </cell>
-          <cell r="B102">
-            <v>2334.742487692165</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103" t="str">
-            <v>M-600</v>
-          </cell>
-          <cell r="B103">
-            <v>58.698162871085799</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104" t="str">
-            <v>M-70-N</v>
-          </cell>
-          <cell r="B104">
-            <v>2410.0600109964689</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105" t="str">
-            <v>M-710</v>
-          </cell>
-          <cell r="B105">
-            <v>988.76926216579295</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106" t="str">
-            <v>M-716</v>
-          </cell>
-          <cell r="B106">
-            <v>795.90900701789189</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107" t="str">
-            <v>M-730-N</v>
-          </cell>
-          <cell r="B107">
-            <v>983.96319621623854</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="A108" t="str">
-            <v>M-750</v>
-          </cell>
-          <cell r="B108">
-            <v>1804.664297686892</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="A109" t="str">
-            <v>M-760-N</v>
-          </cell>
-          <cell r="B109">
-            <v>78.997025515969781</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="A110" t="str">
-            <v>M-80-N</v>
-          </cell>
-          <cell r="B110">
-            <v>15150.509101287529</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="A111" t="str">
-            <v>M-820</v>
-          </cell>
-          <cell r="B111">
-            <v>1154.3303419575391</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="A112" t="str">
-            <v>M-866</v>
-          </cell>
-          <cell r="B112">
-            <v>633.73803887257463</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="A113" t="str">
-            <v>M-890</v>
-          </cell>
-          <cell r="B113">
-            <v>1490.386832849442</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="A114" t="str">
-            <v>M-908</v>
-          </cell>
-          <cell r="B114">
-            <v>2150.879135346036</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="A115" t="str">
-            <v>RUTA 120</v>
-          </cell>
-          <cell r="B115">
-            <v>80930.84814598762</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="A116" t="str">
-            <v>RUTA 126 N</v>
-          </cell>
-          <cell r="B116">
-            <v>457008.72116485192</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="A117" t="str">
-            <v>RUTA 126 S</v>
-          </cell>
-          <cell r="B117">
-            <v>4701.9144853737853</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="A118" t="str">
-            <v>RUTA 128</v>
-          </cell>
-          <cell r="B118">
-            <v>51706.683826834233</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="A119" t="str">
-            <v>Ruta 115 CH</v>
-          </cell>
-          <cell r="B119">
-            <v>2484072.8627775982</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="A120" t="str">
-            <v>S/N</v>
-          </cell>
-          <cell r="B120">
-            <v>1763.9628934977341</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="A121" t="str">
-            <v>S/R</v>
-          </cell>
-          <cell r="B121">
-            <v>4985.3304962660422</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="A122" t="str">
-            <v>S/R L-21</v>
-          </cell>
-          <cell r="B122">
-            <v>101.2050385604113</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="A123" t="str">
-            <v>S/R-K-520</v>
-          </cell>
-          <cell r="B123">
-            <v>120.7216813720631</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="A124" t="str">
-            <v>URBK002</v>
-          </cell>
-          <cell r="B124">
-            <v>18259.698641999999</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="A125" t="str">
-            <v>URBL001</v>
-          </cell>
-          <cell r="B125">
-            <v>64669.007200000007</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1819,12 +807,15 @@
   <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="3"/>
+    <col min="7" max="7" width="12" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1869,9 +860,8 @@
       <c r="F2">
         <v>40.94</v>
       </c>
-      <c r="G2" s="3">
-        <f>LOOKUP(A2,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>7619.0483645064787</v>
+      <c r="G2">
+        <v>15259653.300458919</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1893,9 +883,8 @@
       <c r="F3">
         <v>40.94</v>
       </c>
-      <c r="G3" s="3">
-        <f>LOOKUP(A3,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>10351.93701813308</v>
+      <c r="G3">
+        <v>18880698.582806401</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1917,9 +906,8 @@
       <c r="F4">
         <v>40.94</v>
       </c>
-      <c r="G4" s="3">
-        <f>LOOKUP(A4,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>72200.438137957812</v>
+      <c r="G4">
+        <v>79831426.567284435</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1941,9 +929,8 @@
       <c r="F5">
         <v>40.94</v>
       </c>
-      <c r="G5" s="3">
-        <f>LOOKUP(A5,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>6317.4165120732696</v>
+      <c r="G5">
+        <v>7652094.8052067421</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1965,9 +952,8 @@
       <c r="F6">
         <v>40.94</v>
       </c>
-      <c r="G6" s="3">
-        <f>LOOKUP(A6,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>2262.6284902330058</v>
+      <c r="G6">
+        <v>1821633.207725032</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1989,9 +975,8 @@
       <c r="F7">
         <v>40.94</v>
       </c>
-      <c r="G7" s="3">
-        <f>LOOKUP(A7,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>10164.07724344292</v>
+      <c r="G7">
+        <v>7145904.5183522766</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2013,9 +998,8 @@
       <c r="F8">
         <v>40.94</v>
       </c>
-      <c r="G8" s="3">
-        <f>LOOKUP(A8,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>19368.336953576742</v>
+      <c r="G8">
+        <v>33277138.858162701</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2037,9 +1021,8 @@
       <c r="F9">
         <v>40.94</v>
       </c>
-      <c r="G9" s="3">
-        <f>LOOKUP(A9,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>49815.50482857976</v>
+      <c r="G9">
+        <v>68958116.379334047</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2061,9 +1044,8 @@
       <c r="F10">
         <v>40.94</v>
       </c>
-      <c r="G10" s="3">
-        <f>LOOKUP(A10,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>12250.26732338182</v>
+      <c r="G10">
+        <v>21020589.328194112</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2085,9 +1067,8 @@
       <c r="F11">
         <v>40.94</v>
       </c>
-      <c r="G11" s="3">
-        <f>LOOKUP(A11,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>4948.1140912628043</v>
+      <c r="G11">
+        <v>6595802.2474409603</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -2109,9 +1090,8 @@
       <c r="F12">
         <v>40.94</v>
       </c>
-      <c r="G12" s="3">
-        <f>LOOKUP(A12,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1582.373909739084</v>
+      <c r="G12">
+        <v>1705700.6065235061</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2133,9 +1113,8 @@
       <c r="F13">
         <v>40.94</v>
       </c>
-      <c r="G13" s="3">
-        <f>LOOKUP(A13,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1367.6966510538639</v>
+      <c r="G13">
+        <v>1371281.369787466</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2157,9 +1136,8 @@
       <c r="F14">
         <v>40.94</v>
       </c>
-      <c r="G14" s="3">
-        <f>LOOKUP(A14,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>93919.524354428388</v>
+      <c r="G14">
+        <v>4025864393.9214091</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2181,9 +1159,8 @@
       <c r="F15">
         <v>40.94</v>
       </c>
-      <c r="G15" s="3">
-        <f>LOOKUP(A15,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>11948.086781785079</v>
+      <c r="G15">
+        <v>13645156.301725211</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2205,9 +1182,8 @@
       <c r="F16">
         <v>40.94</v>
       </c>
-      <c r="G16" s="3">
-        <f>LOOKUP(A16,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>189548.06202502971</v>
+      <c r="G16">
+        <v>62302513.687318467</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2229,9 +1205,8 @@
       <c r="F17">
         <v>40.94</v>
       </c>
-      <c r="G17" s="3">
-        <f>LOOKUP(A17,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>3988.1309129103861</v>
+      <c r="G17">
+        <v>4495089.4753058581</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -2253,9 +1228,8 @@
       <c r="F18">
         <v>40.94</v>
       </c>
-      <c r="G18" s="3">
-        <f>LOOKUP(A18,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>3371.0139577269729</v>
+      <c r="G18">
+        <v>4533436.8544040686</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2277,9 +1251,8 @@
       <c r="F19">
         <v>40.94</v>
       </c>
-      <c r="G19" s="3">
-        <f>LOOKUP(A19,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>43024.962376204312</v>
+      <c r="G19">
+        <v>51372180.06724295</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -2301,9 +1274,8 @@
       <c r="F20">
         <v>40.94</v>
       </c>
-      <c r="G20" s="3">
-        <f>LOOKUP(A20,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>5329.4229054158404</v>
+      <c r="G20">
+        <v>6564878.1048850929</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -2325,9 +1297,8 @@
       <c r="F21">
         <v>40.94</v>
       </c>
-      <c r="G21" s="3">
-        <f>LOOKUP(A21,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1304.771666666667</v>
+      <c r="G21">
+        <v>2989397.1765471678</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2349,9 +1320,8 @@
       <c r="F22">
         <v>40.94</v>
       </c>
-      <c r="G22" s="3">
-        <f>LOOKUP(A22,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>8217.7890665854538</v>
+      <c r="G22">
+        <v>7628763.4435815169</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -2373,9 +1343,8 @@
       <c r="F23">
         <v>40.94</v>
       </c>
-      <c r="G23" s="3">
-        <f>LOOKUP(A23,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>5581.8228093440794</v>
+      <c r="G23">
+        <v>6118890.9338686857</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -2397,9 +1366,8 @@
       <c r="F24">
         <v>40.94</v>
       </c>
-      <c r="G24" s="3">
-        <f>LOOKUP(A24,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>21831.927681984271</v>
+      <c r="G24">
+        <v>32551380.56135077</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -2421,9 +1389,8 @@
       <c r="F25">
         <v>40.94</v>
       </c>
-      <c r="G25" s="3">
-        <f>LOOKUP(A25,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>52757.050324769218</v>
+      <c r="G25">
+        <v>67540970.046750426</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2445,9 +1412,8 @@
       <c r="F26">
         <v>40.94</v>
       </c>
-      <c r="G26" s="3">
-        <f>LOOKUP(A26,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>9361.7908776452696</v>
+      <c r="G26">
+        <v>12436828.863971891</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2469,9 +1435,8 @@
       <c r="F27">
         <v>40.94</v>
       </c>
-      <c r="G27" s="3">
-        <f>LOOKUP(A27,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>13815.300838874749</v>
+      <c r="G27">
+        <v>11786784.32948187</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -2493,9 +1458,8 @@
       <c r="F28">
         <v>40.94</v>
       </c>
-      <c r="G28" s="3">
-        <f>LOOKUP(A28,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1435.3962969289489</v>
+      <c r="G28">
+        <v>1300293.165472978</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -2517,9 +1481,8 @@
       <c r="F29">
         <v>40.94</v>
       </c>
-      <c r="G29" s="3">
-        <f>LOOKUP(A29,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>900.52823916286729</v>
+      <c r="G29">
+        <v>1332178.607689884</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2541,9 +1504,8 @@
       <c r="F30">
         <v>40.94</v>
       </c>
-      <c r="G30" s="3">
-        <f>LOOKUP(A30,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>6234.0746979889091</v>
+      <c r="G30">
+        <v>5225174.3339526653</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2565,9 +1527,8 @@
       <c r="F31">
         <v>40.94</v>
       </c>
-      <c r="G31" s="3">
-        <f>LOOKUP(A31,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>3242.3081745541072</v>
+      <c r="G31">
+        <v>2782796.9165583272</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2589,9 +1550,8 @@
       <c r="F32">
         <v>40.94</v>
       </c>
-      <c r="G32" s="3">
-        <f>LOOKUP(A32,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>482.37910440169452</v>
+      <c r="G32">
+        <v>477013.50158060121</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2613,9 +1573,8 @@
       <c r="F33">
         <v>43.05</v>
       </c>
-      <c r="G33" s="3">
-        <f>LOOKUP(A33,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>5992.2399058473693</v>
+      <c r="G33">
+        <v>6128769.5996303689</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -2637,9 +1596,8 @@
       <c r="F34">
         <v>43.05</v>
       </c>
-      <c r="G34" s="3">
-        <f>LOOKUP(A34,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1082.474698389354</v>
+      <c r="G34">
+        <v>1196445.779317403</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2661,9 +1619,8 @@
       <c r="F35">
         <v>43.05</v>
       </c>
-      <c r="G35" s="3">
-        <f>LOOKUP(A35,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>7717.1002948804489</v>
+      <c r="G35">
+        <v>10003778.461689699</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2685,9 +1642,8 @@
       <c r="F36">
         <v>43.04999999999999</v>
       </c>
-      <c r="G36" s="3">
-        <f>LOOKUP(A36,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>726.85382758346645</v>
+      <c r="G36">
+        <v>461901.682011973</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2709,9 +1665,8 @@
       <c r="F37">
         <v>43.05</v>
       </c>
-      <c r="G37" s="3">
-        <f>LOOKUP(A37,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>4104.2270222378784</v>
+      <c r="G37">
+        <v>4093647.297420837</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -2733,9 +1688,8 @@
       <c r="F38">
         <v>43.05</v>
       </c>
-      <c r="G38" s="3">
-        <f>LOOKUP(A38,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>830.36812317638282</v>
+      <c r="G38">
+        <v>728492.04821274988</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -2757,9 +1711,8 @@
       <c r="F39">
         <v>43.05</v>
       </c>
-      <c r="G39" s="3">
-        <f>LOOKUP(A39,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>976.76167199999998</v>
+      <c r="G39">
+        <v>1282197.496166534</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -2781,9 +1734,8 @@
       <c r="F40">
         <v>43.05</v>
       </c>
-      <c r="G40" s="3">
-        <f>LOOKUP(A40,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>179431.96411190819</v>
+      <c r="G40">
+        <v>50360533.615808561</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -2805,9 +1757,8 @@
       <c r="F41">
         <v>43.05</v>
       </c>
-      <c r="G41" s="3">
-        <f>LOOKUP(A41,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>19630.131033602502</v>
+      <c r="G41">
+        <v>23483065.9967076</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -2829,9 +1780,8 @@
       <c r="F42">
         <v>43.05</v>
       </c>
-      <c r="G42" s="3">
-        <f>LOOKUP(A42,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1791.3023261411879</v>
+      <c r="G42">
+        <v>2067964.312845428</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2853,9 +1803,8 @@
       <c r="F43">
         <v>43.04999999999999</v>
       </c>
-      <c r="G43" s="3">
-        <f>LOOKUP(A43,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>724.45718474620548</v>
+      <c r="G43">
+        <v>898287.71308624861</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -2877,9 +1826,8 @@
       <c r="F44">
         <v>43.05</v>
       </c>
-      <c r="G44" s="3">
-        <f>LOOKUP(A44,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>67846.952110057697</v>
+      <c r="G44">
+        <v>34755806.742105082</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2901,9 +1849,8 @@
       <c r="F45">
         <v>43.05</v>
       </c>
-      <c r="G45" s="3">
-        <f>LOOKUP(A45,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>5567.75982729321</v>
+      <c r="G45">
+        <v>4301595.3595000226</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2925,9 +1872,8 @@
       <c r="F46">
         <v>43.05</v>
       </c>
-      <c r="G46" s="3">
-        <f>LOOKUP(A46,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>3532.2193312939939</v>
+      <c r="G46">
+        <v>2818154.8118524551</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2949,9 +1895,8 @@
       <c r="F47">
         <v>43.05</v>
       </c>
-      <c r="G47" s="3">
-        <f>LOOKUP(A47,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1992.403732324485</v>
+      <c r="G47">
+        <v>1035205.021103021</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2973,9 +1918,8 @@
       <c r="F48">
         <v>43.05</v>
       </c>
-      <c r="G48" s="3">
-        <f>LOOKUP(A48,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>850.71241505968783</v>
+      <c r="G48">
+        <v>673603.33778140368</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -2997,9 +1941,8 @@
       <c r="F49">
         <v>43.05</v>
       </c>
-      <c r="G49" s="3">
-        <f>LOOKUP(A49,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>2390.432140429954</v>
+      <c r="G49">
+        <v>1506898.2314013341</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -3021,9 +1964,8 @@
       <c r="F50">
         <v>43.04999999999999</v>
       </c>
-      <c r="G50" s="3">
-        <f>LOOKUP(A50,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>25422.034201961818</v>
+      <c r="G50">
+        <v>11079140.513455831</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -3045,9 +1987,8 @@
       <c r="F51">
         <v>43.05</v>
       </c>
-      <c r="G51" s="3">
-        <f>LOOKUP(A51,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>25422.034201961818</v>
+      <c r="G51">
+        <v>19728016.780526169</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -3069,9 +2010,8 @@
       <c r="F52">
         <v>43.05</v>
       </c>
-      <c r="G52" s="3">
-        <f>LOOKUP(A52,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>3097.7968420897369</v>
+      <c r="G52">
+        <v>2266943.4290692299</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -3093,9 +2033,8 @@
       <c r="F53">
         <v>43.05</v>
       </c>
-      <c r="G53" s="3">
-        <f>LOOKUP(A53,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>2447.8561655805638</v>
+      <c r="G53">
+        <v>2521278.3051690171</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -3117,9 +2056,8 @@
       <c r="F54">
         <v>43.05</v>
       </c>
-      <c r="G54" s="3">
-        <f>LOOKUP(A54,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>9855.9842995581421</v>
+      <c r="G54">
+        <v>9014618.330934355</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -3141,9 +2079,8 @@
       <c r="F55">
         <v>43.05</v>
       </c>
-      <c r="G55" s="3">
-        <f>LOOKUP(A55,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>12856.677238693061</v>
+      <c r="G55">
+        <v>12050599.497317269</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -3165,9 +2102,8 @@
       <c r="F56">
         <v>43.05</v>
       </c>
-      <c r="G56" s="3">
-        <f>LOOKUP(A56,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>7085.7481211057466</v>
+      <c r="G56">
+        <v>8976287.1811711919</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -3189,9 +2125,8 @@
       <c r="F57">
         <v>43.05</v>
       </c>
-      <c r="G57" s="3">
-        <f>LOOKUP(A57,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>55734.761525780843</v>
+      <c r="G57">
+        <v>69761311.96800667</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -3213,9 +2148,8 @@
       <c r="F58">
         <v>43.05</v>
       </c>
-      <c r="G58" s="3">
-        <f>LOOKUP(A58,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>8959.5249647001529</v>
+      <c r="G58">
+        <v>9103807.1435201466</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -3231,9 +2165,8 @@
       <c r="F59">
         <v>43.05</v>
       </c>
-      <c r="G59" s="3">
-        <f>LOOKUP(A59,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>44.585141077055283</v>
+      <c r="G59">
+        <v>152375.80418155721</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -3255,9 +2188,8 @@
       <c r="F60">
         <v>43.04999999999999</v>
       </c>
-      <c r="G60" s="3">
-        <f>LOOKUP(A60,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>69495.254216778834</v>
+      <c r="G60">
+        <v>58078288.935385957</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -3279,9 +2211,8 @@
       <c r="F61">
         <v>43.4</v>
       </c>
-      <c r="G61" s="3">
-        <f>LOOKUP(A61,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>30951.33420428856</v>
+      <c r="G61">
+        <v>42571285.059183858</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -3303,9 +2234,8 @@
       <c r="F62">
         <v>43.4</v>
       </c>
-      <c r="G62" s="3">
-        <f>LOOKUP(A62,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>4102.2215134370581</v>
+      <c r="G62">
+        <v>4469294.9703950007</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -3327,9 +2257,8 @@
       <c r="F63">
         <v>43.4</v>
       </c>
-      <c r="G63" s="3">
-        <f>LOOKUP(A63,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>7665.1918300325251</v>
+      <c r="G63">
+        <v>5286911.3151331507</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -3351,9 +2280,8 @@
       <c r="F64">
         <v>43.4</v>
       </c>
-      <c r="G64" s="3">
-        <f>LOOKUP(A64,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>49652.707851877531</v>
+      <c r="G64">
+        <v>50401475.363837138</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -3375,9 +2303,8 @@
       <c r="F65">
         <v>43.4</v>
       </c>
-      <c r="G65" s="3">
-        <f>LOOKUP(A65,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1649.9862670250361</v>
+      <c r="G65">
+        <v>936653.96099070203</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -3399,9 +2326,8 @@
       <c r="F66">
         <v>43.4</v>
       </c>
-      <c r="G66" s="3">
-        <f>LOOKUP(A66,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>5573.9897451540292</v>
+      <c r="G66">
+        <v>4862230.1879354483</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -3423,9 +2349,8 @@
       <c r="F67">
         <v>43.4</v>
       </c>
-      <c r="G67" s="3">
-        <f>LOOKUP(A67,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>6717.8558496128171</v>
+      <c r="G67">
+        <v>8453820.9344992414</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -3447,9 +2372,8 @@
       <c r="F68">
         <v>43.4</v>
       </c>
-      <c r="G68" s="3">
-        <f>LOOKUP(A68,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>3673.9642246980379</v>
+      <c r="G68">
+        <v>3916138.4672280378</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -3471,9 +2395,8 @@
       <c r="F69">
         <v>43.4</v>
       </c>
-      <c r="G69" s="3">
-        <f>LOOKUP(A69,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>253.85420844413801</v>
+      <c r="G69">
+        <v>293920.78740772</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -3495,9 +2418,8 @@
       <c r="F70">
         <v>43.4</v>
       </c>
-      <c r="G70" s="3">
-        <f>LOOKUP(A70,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>35665.43809510018</v>
+      <c r="G70">
+        <v>44218053.567380451</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
@@ -3519,9 +2441,8 @@
       <c r="F71">
         <v>43.4</v>
       </c>
-      <c r="G71" s="3">
-        <f>LOOKUP(A71,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>5089.8657090909073</v>
+      <c r="G71">
+        <v>4226395.8682120219</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -3543,9 +2464,8 @@
       <c r="F72">
         <v>43.4</v>
       </c>
-      <c r="G72" s="3">
-        <f>LOOKUP(A72,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>2807.8942847058411</v>
+      <c r="G72">
+        <v>1393994.9074567959</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -3567,9 +2487,8 @@
       <c r="F73">
         <v>43.4</v>
       </c>
-      <c r="G73" s="3">
-        <f>LOOKUP(A73,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>149104.5441978325</v>
+      <c r="G73">
+        <v>314811827.9464522</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -3591,9 +2510,8 @@
       <c r="F74">
         <v>43.4</v>
       </c>
-      <c r="G74" s="3">
-        <f>LOOKUP(A74,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>9449.1127267722532</v>
+      <c r="G74">
+        <v>13849107.011666089</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -3615,9 +2533,8 @@
       <c r="F75">
         <v>43.4</v>
       </c>
-      <c r="G75" s="3">
-        <f>LOOKUP(A75,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>15335.356975078999</v>
+      <c r="G75">
+        <v>19881868.6767007</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -3639,9 +2556,8 @@
       <c r="F76">
         <v>43.4</v>
       </c>
-      <c r="G76" s="3">
-        <f>LOOKUP(A76,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1355.5832818502481</v>
+      <c r="G76">
+        <v>1329924.1795266131</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
@@ -3663,9 +2579,8 @@
       <c r="F77">
         <v>43.4</v>
       </c>
-      <c r="G77" s="3">
-        <f>LOOKUP(A77,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>7045.1438083273497</v>
+      <c r="G77">
+        <v>3103003.3791725701</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -3687,9 +2602,8 @@
       <c r="F78">
         <v>43.4</v>
       </c>
-      <c r="G78" s="3">
-        <f>LOOKUP(A78,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1100.3449358375769</v>
+      <c r="G78">
+        <v>1707954.6010056969</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -3711,9 +2625,8 @@
       <c r="F79">
         <v>43.4</v>
       </c>
-      <c r="G79" s="3">
-        <f>LOOKUP(A79,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>287.74363818456021</v>
+      <c r="G79">
+        <v>570694.29224555974</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -3735,9 +2648,8 @@
       <c r="F80">
         <v>43.4</v>
       </c>
-      <c r="G80" s="3">
-        <f>LOOKUP(A80,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>614.5167396174337</v>
+      <c r="G80">
+        <v>1157274.7433225161</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -3759,9 +2671,8 @@
       <c r="F81">
         <v>43.4</v>
       </c>
-      <c r="G81" s="3">
-        <f>LOOKUP(A81,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>2993.828399940784</v>
+      <c r="G81">
+        <v>2129478.2135957102</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -3783,9 +2694,8 @@
       <c r="F82">
         <v>43.4</v>
       </c>
-      <c r="G82" s="3">
-        <f>LOOKUP(A82,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1043.4499458197879</v>
+      <c r="G82">
+        <v>1200998.413840746</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -3807,9 +2717,8 @@
       <c r="F83">
         <v>43.4</v>
       </c>
-      <c r="G83" s="3">
-        <f>LOOKUP(A83,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>9739.9071363956209</v>
+      <c r="G83">
+        <v>7619222.9014475793</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -3831,9 +2740,8 @@
       <c r="F84">
         <v>43.4</v>
       </c>
-      <c r="G84" s="3">
-        <f>LOOKUP(A84,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>500.1647038676619</v>
+      <c r="G84">
+        <v>409347.92433509917</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -3855,9 +2763,8 @@
       <c r="F85">
         <v>43.4</v>
       </c>
-      <c r="G85" s="3">
-        <f>LOOKUP(A85,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>5830.6457879304053</v>
+      <c r="G85">
+        <v>5728575.7302719681</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -3879,9 +2786,8 @@
       <c r="F86">
         <v>43.4</v>
       </c>
-      <c r="G86" s="3">
-        <f>LOOKUP(A86,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>350.63398610770378</v>
+      <c r="G86">
+        <v>1019165.115558163</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -3903,9 +2809,8 @@
       <c r="F87">
         <v>43.4</v>
       </c>
-      <c r="G87" s="3">
-        <f>LOOKUP(A87,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>6122.4369765857291</v>
+      <c r="G87">
+        <v>8110487.720752866</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3927,9 +2832,8 @@
       <c r="F88">
         <v>43.4</v>
       </c>
-      <c r="G88" s="3">
-        <f>LOOKUP(A88,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>20257.88498724798</v>
+      <c r="G88">
+        <v>24642058.038372058</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -3951,9 +2855,8 @@
       <c r="F89">
         <v>43.4</v>
       </c>
-      <c r="G89" s="3">
-        <f>LOOKUP(A89,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>8347.4716027707109</v>
+      <c r="G89">
+        <v>5086366.0473764213</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -3975,9 +2878,8 @@
       <c r="F90">
         <v>43.4</v>
       </c>
-      <c r="G90" s="3">
-        <f>LOOKUP(A90,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>2400.4270235909471</v>
+      <c r="G90">
+        <v>1066146.928275537</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -3999,9 +2901,8 @@
       <c r="F91">
         <v>43.4</v>
       </c>
-      <c r="G91" s="3">
-        <f>LOOKUP(A91,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1225.552589242749</v>
+      <c r="G91">
+        <v>1287902.552960163</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -4023,9 +2924,8 @@
       <c r="F92">
         <v>43.4</v>
       </c>
-      <c r="G92" s="3">
-        <f>LOOKUP(A92,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>312426.03767695627</v>
+      <c r="G92">
+        <v>66336309.441231638</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -4047,9 +2947,8 @@
       <c r="F93">
         <v>43.4</v>
       </c>
-      <c r="G93" s="3">
-        <f>LOOKUP(A93,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>9211.3752871367524</v>
+      <c r="G93">
+        <v>14809110.879084481</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -4071,9 +2970,8 @@
       <c r="F94">
         <v>43.4</v>
       </c>
-      <c r="G94" s="3">
-        <f>LOOKUP(A94,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1218.450561052719</v>
+      <c r="G94">
+        <v>1778393.123203251</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -4095,9 +2993,8 @@
       <c r="F95">
         <v>43.4</v>
       </c>
-      <c r="G95" s="3">
-        <f>LOOKUP(A95,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>7647.8277402915446</v>
+      <c r="G95">
+        <v>9117194.9938995056</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -4119,9 +3016,8 @@
       <c r="F96">
         <v>43.4</v>
       </c>
-      <c r="G96" s="3">
-        <f>LOOKUP(A96,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1560.984478666013</v>
+      <c r="G96">
+        <v>1470649.477685974</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -4143,9 +3039,8 @@
       <c r="F97">
         <v>31.3</v>
       </c>
-      <c r="G97" s="3">
-        <f>LOOKUP(A97,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>255.467650523966</v>
+      <c r="G97">
+        <v>636079.04107728414</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -4167,9 +3062,8 @@
       <c r="F98">
         <v>31.3</v>
       </c>
-      <c r="G98" s="3">
-        <f>LOOKUP(A98,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>350.27415493806342</v>
+      <c r="G98">
+        <v>378282.281528313</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -4191,9 +3085,8 @@
       <c r="F99">
         <v>31.3</v>
       </c>
-      <c r="G99" s="3">
-        <f>LOOKUP(A99,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1582.0808604981021</v>
+      <c r="G99">
+        <v>91401598.498194367</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -4215,9 +3108,8 @@
       <c r="F100">
         <v>31.3</v>
       </c>
-      <c r="G100" s="3">
-        <f>LOOKUP(A100,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1582.0808604981021</v>
+      <c r="G100">
+        <v>3890195.4912006902</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -4239,9 +3131,8 @@
       <c r="F101">
         <v>31.3</v>
       </c>
-      <c r="G101" s="3">
-        <f>LOOKUP(A101,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1303.402855759472</v>
+      <c r="G101">
+        <v>2422610.26729646</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
@@ -4263,9 +3154,8 @@
       <c r="F102">
         <v>31.3</v>
       </c>
-      <c r="G102" s="3">
-        <f>LOOKUP(A102,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>2334.742487692165</v>
+      <c r="G102">
+        <v>2108975.6879747231</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -4287,9 +3177,8 @@
       <c r="F103">
         <v>31.3</v>
       </c>
-      <c r="G103" s="3">
-        <f>LOOKUP(A103,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>58.698162871085799</v>
+      <c r="G103">
+        <v>111330.0217874556</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
@@ -4311,9 +3200,8 @@
       <c r="F104">
         <v>31.3</v>
       </c>
-      <c r="G104" s="3">
-        <f>LOOKUP(A104,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>2410.0600109964689</v>
+      <c r="G104">
+        <v>3165410.4355739802</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -4335,9 +3223,8 @@
       <c r="F105">
         <v>31.3</v>
       </c>
-      <c r="G105" s="3">
-        <f>LOOKUP(A105,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>988.76926216579295</v>
+      <c r="G105">
+        <v>572135.68584406574</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
@@ -4359,9 +3246,8 @@
       <c r="F106">
         <v>31.3</v>
       </c>
-      <c r="G106" s="3">
-        <f>LOOKUP(A106,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>795.90900701789189</v>
+      <c r="G106">
+        <v>361576.21761051338</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
@@ -4383,9 +3269,8 @@
       <c r="F107">
         <v>31.3</v>
       </c>
-      <c r="G107" s="3">
-        <f>LOOKUP(A107,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>983.96319621623854</v>
+      <c r="G107">
+        <v>1555622.1418909831</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -4407,9 +3292,8 @@
       <c r="F108">
         <v>31.3</v>
       </c>
-      <c r="G108" s="3">
-        <f>LOOKUP(A108,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1804.664297686892</v>
+      <c r="G108">
+        <v>2348286.200303908</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
@@ -4431,9 +3315,8 @@
       <c r="F109">
         <v>31.3</v>
       </c>
-      <c r="G109" s="3">
-        <f>LOOKUP(A109,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>78.997025515969781</v>
+      <c r="G109">
+        <v>96301.121487279655</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
@@ -4455,9 +3338,8 @@
       <c r="F110">
         <v>31.3</v>
       </c>
-      <c r="G110" s="3">
-        <f>LOOKUP(A110,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>15150.509101287529</v>
+      <c r="G110">
+        <v>11597398.234666791</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
@@ -4479,9 +3361,8 @@
       <c r="F111">
         <v>31.3</v>
       </c>
-      <c r="G111" s="3">
-        <f>LOOKUP(A111,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1154.3303419575391</v>
+      <c r="G111">
+        <v>1051881.1386466341</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
@@ -4503,9 +3384,8 @@
       <c r="F112">
         <v>31.3</v>
       </c>
-      <c r="G112" s="3">
-        <f>LOOKUP(A112,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>633.73803887257463</v>
+      <c r="G112">
+        <v>804497.02105737396</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
@@ -4527,9 +3407,8 @@
       <c r="F113">
         <v>31.3</v>
       </c>
-      <c r="G113" s="3">
-        <f>LOOKUP(A113,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1490.386832849442</v>
+      <c r="G113">
+        <v>1722907.5731614321</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
@@ -4551,9 +3430,8 @@
       <c r="F114">
         <v>31.3</v>
       </c>
-      <c r="G114" s="3">
-        <f>LOOKUP(A114,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>2150.879135346036</v>
+      <c r="G114">
+        <v>1910223.427193135</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
@@ -4575,9 +3453,8 @@
       <c r="F115">
         <v>43.05</v>
       </c>
-      <c r="G115" s="3">
-        <f>LOOKUP(A115,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>2150.879135346036</v>
+      <c r="G115">
+        <v>680044221.25170183</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
@@ -4599,9 +3476,8 @@
       <c r="F116">
         <v>43.05</v>
       </c>
-      <c r="G116" s="3">
-        <f>LOOKUP(A116,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>80930.84814598762</v>
+      <c r="G116">
+        <v>73725107.245077699</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
@@ -4623,9 +3499,8 @@
       <c r="F117">
         <v>43.05</v>
       </c>
-      <c r="G117" s="3">
-        <f>LOOKUP(A117,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>457008.72116485192</v>
+      <c r="G117">
+        <v>207202065.77923709</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
@@ -4647,9 +3522,8 @@
       <c r="F118">
         <v>31.3</v>
       </c>
-      <c r="G118" s="3">
-        <f>LOOKUP(A118,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>4701.9144853737853</v>
+      <c r="G118">
+        <v>10397992.704802649</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
@@ -4671,9 +3545,8 @@
       <c r="F119">
         <v>31.3</v>
       </c>
-      <c r="G119" s="3">
-        <f>LOOKUP(A119,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>51706.683826834233</v>
+      <c r="G119">
+        <v>77816366.472178489</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
@@ -4695,9 +3568,8 @@
       <c r="F120">
         <v>43.05</v>
       </c>
-      <c r="G120" s="3">
-        <f>LOOKUP(A120,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>18259.698641999999</v>
+      <c r="G120">
+        <v>25861351.056880452</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
@@ -4719,9 +3591,8 @@
       <c r="F121">
         <v>43.4</v>
       </c>
-      <c r="G121" s="3">
-        <f>LOOKUP(A121,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>64669.007200000007</v>
+      <c r="G121">
+        <v>68301683.902102232</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
@@ -4743,9 +3614,8 @@
       <c r="F122">
         <v>43.05</v>
       </c>
-      <c r="G122" s="3">
-        <f>LOOKUP(A122,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
-        <v>1082.474698389354</v>
+      <c r="G122">
+        <v>1196445.779317403</v>
       </c>
     </row>
   </sheetData>
